--- a/history_prices/JUNE/prices_24062026.xlsx
+++ b/history_prices/JUNE/prices_24062026.xlsx
@@ -11069,6 +11069,80 @@
         </is>
       </c>
     </row>
+    <row r="269" ht="19.2" customHeight="1">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>0413</t>
+        </is>
+      </c>
+      <c r="B269" s="1" t="n">
+        <v>46197</v>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>СИЙД ЕКСПРЕС ЕООД</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>Diesel EKONOMY</t>
+        </is>
+      </c>
+      <c r="E269" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F269" s="3" t="n">
+        <v>1.429</v>
+      </c>
+      <c r="G269" s="3" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H269" s="2" t="n">
+        <v>1.439</v>
+      </c>
+      <c r="N269" t="inlineStr">
+        <is>
+          <t>205091212</t>
+        </is>
+      </c>
+    </row>
+    <row r="270" ht="19.2" customHeight="1">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>0414</t>
+        </is>
+      </c>
+      <c r="B270" s="1" t="n">
+        <v>46197</v>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>СИЙД ЕКСПРЕС ЕООД</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>95 EKONOMY Unleaded</t>
+        </is>
+      </c>
+      <c r="E270" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F270" s="3" t="n">
+        <v>1.379</v>
+      </c>
+      <c r="G270" s="3" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H270" s="2" t="n">
+        <v>1.399</v>
+      </c>
+      <c r="N270" t="inlineStr">
+        <is>
+          <t>205091212</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
